--- a/logs/encoders/5runs/random_seed_runs.xlsx
+++ b/logs/encoders/5runs/random_seed_runs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddore/Documents/RooseBERT/logs/encoders/5runs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BEEA38-5CD0-5E4E-B87B-556D6442783D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222F6C70-4786-A346-BDF1-66CEB4DBD5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="multi_class_ParlVotePlus" sheetId="1" r:id="rId1"/>
@@ -23,13 +23,14 @@
     <sheet name="binary_AusHansard" sheetId="8" r:id="rId8"/>
     <sheet name="multi_class_ArgUNSC" sheetId="9" r:id="rId9"/>
     <sheet name="binary_HanDeSet" sheetId="10" r:id="rId10"/>
+    <sheet name="ner_nerex" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="160">
   <si>
     <t>Models</t>
   </si>
@@ -46,9 +47,6 @@
     <t>polibertweet-political-twitter-roberta-mlm</t>
   </si>
   <si>
-    <t>[0.4143566210293423, 0.0100353446099469, 0.0100353446099469, 0.4258518593701578, 0.003213352197789]</t>
-  </si>
-  <si>
     <t>ConfliBERT-scr-cased</t>
   </si>
   <si>
@@ -70,9 +68,6 @@
     <t>ConfliBERT-cont-uncased</t>
   </si>
   <si>
-    <t>[0.5585934421522584, 0.5584331412040209, 0.0012415265810841, 0.5683596747739865, 0.5297593558698709]</t>
-  </si>
-  <si>
     <t>roberta-base</t>
   </si>
   <si>
@@ -100,7 +95,7 @@
     <t>bert-base-cased</t>
   </si>
   <si>
-    <t>[0.5365892314099252, 0.5509684268484881, 0.5198272681750576, 0.003995649706828, 0.5483212135594939]</t>
+    <t>[0.5291862854158778, 0.5509684268484881, 0.5198272681750576, 0.5445396029930457, 0.5359910180665641]</t>
   </si>
   <si>
     <t>ConfliBERT-scr-uncased</t>
@@ -112,13 +107,10 @@
     <t>NEWRooseBERT-cont-cased</t>
   </si>
   <si>
-    <t>[0.5782344815563583, 0.0026870007262164, 0.5564985431303056, 0.574140869959322, 0.5797136367409205]</t>
-  </si>
-  <si>
     <t>bert-base-uncased</t>
   </si>
   <si>
-    <t>[0.5535268015798916, 0.5468327912127925, 0.0018428424001179, 0.5656902883929769, 0.5464250963685272]</t>
+    <t>[0.5479242428191978, 0.5429902373740095, 0.5362952934328681, 0.5528676080769837, 0.5589441787887326]</t>
   </si>
   <si>
     <t>[0.6550836550836551, 0.6833976833976834, 0.7014157014157014, 0.6808236808236808, 0.6898326898326899]</t>
@@ -286,9 +278,6 @@
     <t>[0.6103023238518073, 0.6194920686902864, 0.604791792397032, 0.6208680647957662, 0.6106134075894539]</t>
   </si>
   <si>
-    <t>[0.6167572816076136, 0.6154255756764593, 0.6150923098163601, 0.6209175422277808, 0.6074491326437897]</t>
-  </si>
-  <si>
     <t>[0.6141790889727938, 0.6079004084275917, 0.5905032484277789, 0.5909868452756812, 0.6052079758819078]</t>
   </si>
   <si>
@@ -301,12 +290,6 @@
     <t>[0.619710011678541, 0.6032229492137294, 0.597788246415832, 0.611978582820003, 0.614152841171168]</t>
   </si>
   <si>
-    <t>[0.620758403824424, 0.6102427948112207, 0.6260756989995003, 0.6155104533169825, 0.6166136904400832]</t>
-  </si>
-  <si>
-    <t>[0.6139867728888098, 0.6133133913455123, 0.5904062738345675, 0.6125268943178438, 0.6241332035489668]</t>
-  </si>
-  <si>
     <t>[0.6038859434276633, 0.5920253644688493, 0.6140511068086081, 0.5976780022235458, 0.596127634275472]</t>
   </si>
   <si>
@@ -388,6 +371,9 @@
     <t>[0.5886889460154242, 0.5861182519280206, 0.5989717223650386, 0.570694087403599, 0.5976863753213367]</t>
   </si>
   <si>
+    <t>[0.622107969151671, 0.6182519280205655, 0.6182519280205655, 0.6118251928020566, 0.6105398457583547]</t>
+  </si>
+  <si>
     <t>[0.5462724935732648, 0.538560411311054, 0.5719794344473008, 0.5668380462724936, 0.5308483290488432]</t>
   </si>
   <si>
@@ -400,15 +386,15 @@
     <t>[0.6952187639119624, 0.7314795588778148, 0.7171193512949343, 0.6530409589562369, 0.7470015369846738]</t>
   </si>
   <si>
-    <t>[0.2672790901137358, 0.2672790901137358, 0.6656019973350104, 0.6884658616217673, 0.675876279741014]</t>
-  </si>
-  <si>
     <t>[0.6578369605790609, 0.6537739299243437, 0.2882879185817465, 0.6270826391079556, 0.6281772162749717]</t>
   </si>
   <si>
     <t>[0.7189838747393754, 0.7100148020884157, 0.3086622333177878, 0.6669969785364361, 0.7310734679742789]</t>
   </si>
   <si>
+    <t>[0.7006606483536917, 0.7247682075268282, 0.705949578177476, 0.7590320371153895, 0.7039103153086911]</t>
+  </si>
+  <si>
     <t>[0.7160367943640739, 0.4781217631104928, 0.4047237484737485, 0.7495110588750772, 0.695246996986646]</t>
   </si>
   <si>
@@ -424,7 +410,7 @@
     <t>[0.6892209768922098, 0.495129295228565, 0.673913788785493, 0.15259009009009, 0.7012849162111374]</t>
   </si>
   <si>
-    <t>[0.621726732192695, 0.6681338540087105, 0.6041785277513695, 0.2672790901137358, 0.6643794557363331]</t>
+    <t>[0.621726732192695, 0.6681338540087105, 0.6010980204323538, 0.6439971702147366, 0.6643794557363331]</t>
   </si>
   <si>
     <t>[0.5725806451612904, 0.6774193548387096, 0.6370967741935484, 0.4596774193548387, 0.6532258064516129]</t>
@@ -466,10 +452,64 @@
     <t>[0.6774193548387096, 0.7016129032258065, 0.5967741935483871, 0.6532258064516129, 0.6935483870967742]</t>
   </si>
   <si>
-    <t>[0.7006606483536917, 0.7247682075268282, 0.705949578177476, 0.7590320371153895, 0.7039103153086911]</t>
-  </si>
-  <si>
-    <t>[0.622107969151671, 0.6182519280205655, 0.6182519280205655, 0.6118251928020566, 0.6105398457583547]</t>
+    <t>[0.5474089421110534, 0.5584331412040209, 0.560119242052707, 0.5683596747739865, 0.5297593558698709]</t>
+  </si>
+  <si>
+    <t>[0.6139867728888098, 0.6133133913455123, 0.5904062738345675, 0.6060964760877843, 0.6178916680419652]</t>
+  </si>
+  <si>
+    <t>[0.2672790901137358, 0.4932873290370807, 0.6469240633341237, 0.6884658616217673, 0.675876279741014]</t>
+  </si>
+  <si>
+    <t>[0.6133612116718671, 0.6154255756764593, 0.6150923098163601, 0.6094162085477175, 0.6074491326437897]</t>
+  </si>
+  <si>
+    <t>[0.5782344815563583, 0.583280148448151, 0.5564985431303056, 0.574140869959322, 0.5797136367409205]</t>
+  </si>
+  <si>
+    <t>[0.4143566210293423, 0.4290991472570353, 0.4250150433985475, 0.4258518593701578, 0.0100353446099469]</t>
+  </si>
+  <si>
+    <t>[0.620758403824424, 0.6102427948112207, 0.6260756989995003, 0.6189194187379682, 0.6282033394735198]</t>
+  </si>
+  <si>
+    <t>[0.8852653948963465, 0.8868233960478341, 0.8846506904534458, 0.8547962388064577, 0.8888354143567941]</t>
+  </si>
+  <si>
+    <t>[0.926353214171392, 0.9218422912316424, 0.8945061310710603, 0.9127656863529178, 0.895850408829463]</t>
+  </si>
+  <si>
+    <t>[0.9104788107627132, 0.9101409988488952, 0.8858929647154464, 0.8855280415528075, 0.92160034652834]</t>
+  </si>
+  <si>
+    <t>[0.9106051661732424, 0.9081270030814595, 0.9078332285772868, 0.906926037417063, 0.918624180342036]</t>
+  </si>
+  <si>
+    <t>[0.9241178783042178, 0.896868006330897, 0.895739294277255, 0.9154295607207704, 0.9213849146171944]</t>
+  </si>
+  <si>
+    <t>[0.9156638136535938, 0.9147455763688978, 0.8948353489930498, 0.9042574876379428, 0.9047211415884568]</t>
+  </si>
+  <si>
+    <t>[0.9076133596737632, 0.9051631284323046, 0.9065490419915831, 0.8984716373538927, 0.8903024914233841]</t>
+  </si>
+  <si>
+    <t>[0.9197634373293836, 0.9100744424238454, 0.9218018685154482, 0.911963406954432, 0.9233646338571352]</t>
+  </si>
+  <si>
+    <t>[0.9207137746849596, 0.9080664166538692, 0.9200854252358588, 0.9127708411678934, 0.9113959334682616]</t>
+  </si>
+  <si>
+    <t>[0.9176285653365024, 0.908862371856114, 0.9085832050141424, 0.8996057179852217, 0.90805519761828]</t>
+  </si>
+  <si>
+    <t>[0.9178564957394711, 0.9097728779542328, 0.8788089078698402, 0.9079564289879156, 0.9089032876607428]</t>
+  </si>
+  <si>
+    <t>[0.919750523061362, 0.9165799403378176, 0.9152310674654132, 0.9164817839177796, 0.9165453977827052]</t>
+  </si>
+  <si>
+    <t>[0.9218906929755366, 0.9201273015915984, 0.9178126467228844, 0.918532717607032, 0.9186073667824262]</t>
   </si>
 </sst>
 </file>
@@ -486,6 +526,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="14"/>
       <name val="Calibri (Corpo)"/>
     </font>
@@ -493,13 +539,6 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri (Corpo)"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
@@ -518,7 +557,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,21 +589,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -867,6 +903,427 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="4" customFormat="1" ht="19" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="C3" s="2">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="C4" s="2">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="C7" s="2">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.45400000000000001</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.249</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="C10" s="2">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1.9E-2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="C12" s="2">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="6">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.185</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="6" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
+    <sortCondition ref="A1:A14"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.6</v>
+      </c>
+      <c r="C2">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>0.65</v>
+      </c>
+      <c r="C3">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="C4">
+        <v>0.03</v>
+      </c>
+      <c r="D4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>0.64700000000000002</v>
+      </c>
+      <c r="C5">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>0.65300000000000002</v>
+      </c>
+      <c r="C6">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="C7">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="C8">
+        <v>2.3E-2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="C9">
+        <v>1.6E-2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="C10">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="C11">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="C12">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="C13">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="C14">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E9504E-C2C3-E74A-8F22-B4B0846DE9C3}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
@@ -876,7 +1333,7 @@
     <col min="5" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -892,16 +1349,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>0.61899999999999999</v>
+        <v>0.91900000000000004</v>
       </c>
       <c r="C2" s="2">
-        <v>7.0000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -909,13 +1366,13 @@
         <v>18</v>
       </c>
       <c r="B3" s="2">
-        <v>0.61199999999999999</v>
+        <v>0.91700000000000004</v>
       </c>
       <c r="C3" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -923,139 +1380,139 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>0.61099999999999999</v>
+        <v>0.91700000000000004</v>
       </c>
       <c r="C4" s="2">
-        <v>1.9E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
-        <v>0.59099999999999997</v>
+        <v>0.91500000000000004</v>
       </c>
       <c r="C5" s="2">
-        <v>7.0000000000000001E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2">
-        <v>0.57699999999999996</v>
+        <v>0.91100000000000003</v>
       </c>
       <c r="C6" s="2">
-        <v>7.0000000000000001E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>0.57399999999999995</v>
+        <v>0.91</v>
       </c>
       <c r="C7" s="2">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>0.45800000000000002</v>
+        <v>0.91</v>
       </c>
       <c r="C8" s="2">
-        <v>0.255</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2">
-        <v>0.45500000000000002</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="C9" s="2">
-        <v>0.23200000000000001</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2">
-        <v>0.45400000000000001</v>
+        <v>0.90700000000000003</v>
       </c>
       <c r="C10" s="2">
-        <v>0.249</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2">
-        <v>0.443</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="C11" s="2">
-        <v>0.248</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2">
-        <v>0.443</v>
+        <v>0.90300000000000002</v>
       </c>
       <c r="C12" s="2">
-        <v>0.247</v>
+        <v>1.6E-2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
-        <v>0.432</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="C13" s="2">
-        <v>0.24</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1063,228 +1520,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>0.17299999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="C14" s="2">
-        <v>0.22600000000000001</v>
+        <v>1.4E-2</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
-    <sortCondition descending="1" ref="B1:B14"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="42.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0.73099999999999998</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.71499999999999997</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.70499999999999996</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2.3E-2</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0.69399999999999995</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1.6E-2</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.67300000000000004</v>
-      </c>
-      <c r="C6" s="2">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0.66500000000000004</v>
-      </c>
-      <c r="C7" s="2">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0.65800000000000003</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0.65300000000000002</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1.2E-2</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.64700000000000002</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1.2E-2</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.64200000000000002</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0.63400000000000001</v>
-      </c>
-      <c r="C13" s="2">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="C14" s="2">
-        <v>8.7999999999999995E-2</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1298,15 +1540,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="4" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1320,65 +1561,65 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>0.77300000000000002</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="C2" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2">
-        <v>0.77200000000000002</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="C3" s="2">
-        <v>8.0000000000000002E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
-        <v>0.76900000000000002</v>
+        <v>0.752</v>
       </c>
       <c r="C4" s="2">
-        <v>1.2999999999999999E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
-        <v>0.753</v>
+        <v>0.748</v>
       </c>
       <c r="C5" s="2">
-        <v>8.9999999999999993E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
         <v>0.752</v>
@@ -1387,124 +1628,124 @@
         <v>0.01</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
       <c r="C7" s="2">
-        <v>5.0000000000000001E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2">
-        <v>0.749</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="B9" s="2">
-        <v>0.748</v>
+        <v>0.745</v>
       </c>
       <c r="C9" s="2">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.745</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2">
-        <v>0.74299999999999999</v>
+        <v>0.77200000000000002</v>
       </c>
       <c r="C11" s="2">
-        <v>2.1999999999999999E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>0.72699999999999998</v>
+        <v>0.77300000000000002</v>
       </c>
       <c r="C12" s="2">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>0.72299999999999998</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="C13" s="2">
-        <v>7.0000000000000001E-3</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.68200000000000005</v>
+        <v>0.753</v>
       </c>
       <c r="C14" s="2">
-        <v>1.7000000000000001E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
-    <sortCondition descending="1" ref="B1:B14"/>
+    <sortCondition ref="A1:A14"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1513,214 +1754,205 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="42.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="2"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.27</v>
+      </c>
+      <c r="C2">
+        <v>0.02</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="C3">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>0.188</v>
+      </c>
+      <c r="C4">
+        <v>0.113</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
         <v>0.39</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C5">
         <v>0.04</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>0.377</v>
+      </c>
+      <c r="C6">
+        <v>0.05</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="C7">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>0.191</v>
+      </c>
+      <c r="C8">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.377</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>0.255</v>
+      </c>
+      <c r="C9">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>0.312</v>
+      </c>
+      <c r="C10">
+        <v>4.7E-2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2">
-        <v>0.312</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="B11">
+        <v>0.192</v>
+      </c>
+      <c r="C11">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12">
+        <v>0.11</v>
+      </c>
+      <c r="C12">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="C13">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
+        <v>0.251</v>
+      </c>
+      <c r="C14">
         <v>4.7E-2</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="C5" s="2">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.27</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0.255</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0.251</v>
-      </c>
-      <c r="C8" s="2">
-        <v>4.7E-2</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0.192</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.11899999999999999</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="D14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.191</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.188</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.113</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.13700000000000001</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="2">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
-    <sortCondition descending="1" ref="B1:B14"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1736,7 +1968,7 @@
     <col min="5" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1755,153 +1987,153 @@
         <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>0.80200000000000005</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="C2" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>2.3E-2</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2">
-        <v>0.8</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="C3" s="2">
-        <v>3.0000000000000001E-3</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
-        <v>0.8</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="C4" s="2">
-        <v>8.9999999999999993E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
-        <v>0.78500000000000003</v>
+        <v>0.752</v>
       </c>
       <c r="C5" s="2">
-        <v>7.0000000000000001E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>0.76600000000000001</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="C6" s="2">
-        <v>1.0999999999999999E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2">
-        <v>0.76300000000000001</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="C7" s="2">
-        <v>8.0000000000000002E-3</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>0.752</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="C8" s="2">
-        <v>8.0000000000000002E-3</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2">
-        <v>0.74199999999999999</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="C9" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2">
-        <v>0.74199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="C10" s="2">
-        <v>1.7000000000000001E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2">
-        <v>0.68799999999999994</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="C11" s="2">
-        <v>2.3E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>0.67100000000000004</v>
+        <v>0.8</v>
       </c>
       <c r="C12" s="2">
-        <v>7.9000000000000001E-2</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1915,18 +2147,18 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.57599999999999996</v>
+        <v>0.76600000000000001</v>
       </c>
       <c r="C14" s="2">
-        <v>9.6000000000000002E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>58</v>
@@ -1934,7 +2166,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
-    <sortCondition descending="1" ref="B1:B14"/>
+    <sortCondition ref="A1:A14"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1943,15 +2175,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="4" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1965,191 +2196,191 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>0.63400000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="C2" s="2">
-        <v>3.0000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2">
-        <v>0.628</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="C3" s="2">
-        <v>2E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
-        <v>0.626</v>
+        <v>0.624</v>
       </c>
       <c r="C4" s="2">
-        <v>3.0000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
-        <v>0.626</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="C5" s="2">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
         <v>0.626</v>
       </c>
       <c r="C6" s="2">
-        <v>2E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2">
-        <v>0.625</v>
+        <v>0.626</v>
       </c>
       <c r="C7" s="2">
-        <v>2E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
+        <v>0.628</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2E-3</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.626</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2E-3</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2">
         <v>0.625</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0.624</v>
-      </c>
-      <c r="C9" s="2">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.622</v>
       </c>
       <c r="C10" s="2">
         <v>2E-3</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="C13" s="2">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="2">
-        <v>0.61899999999999999</v>
-      </c>
-      <c r="C11" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.61</v>
-      </c>
-      <c r="C12" s="2">
+      <c r="B14" s="2">
+        <v>0.622</v>
+      </c>
+      <c r="C14" s="2">
         <v>2E-3</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0.60599999999999998</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0.59499999999999997</v>
-      </c>
-      <c r="C14" s="2">
-        <v>8.9999999999999993E-3</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
-    <sortCondition descending="1" ref="B1:B14"/>
+    <sortCondition ref="A1:A14"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2166,205 +2397,205 @@
     <col min="5" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.61799999999999999</v>
-      </c>
-      <c r="C2" s="2">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>90</v>
+      <c r="B2" s="6">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2">
-        <v>0.61599999999999999</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="C3" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.61499999999999999</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>85</v>
+      <c r="A4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="C4" s="6">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
-        <v>0.61399999999999999</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="C5" s="2">
-        <v>7.0000000000000001E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>0.61299999999999999</v>
+        <v>0.61199999999999999</v>
       </c>
       <c r="C6" s="2">
-        <v>7.0000000000000001E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2">
-        <v>0.61199999999999999</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="C7" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>0.61099999999999999</v>
+        <v>0.61299999999999999</v>
       </c>
       <c r="C8" s="2">
-        <v>1.2E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2">
-        <v>0.60899999999999999</v>
+        <v>0.61399999999999999</v>
       </c>
       <c r="C9" s="2">
-        <v>8.9999999999999993E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2">
-        <v>0.60599999999999998</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="C10" s="2">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.60299999999999998</v>
-      </c>
-      <c r="C11" s="2">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>88</v>
+      <c r="A11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="6">
+        <v>0.621</v>
+      </c>
+      <c r="C11" s="6">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>0.60199999999999998</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="C12" s="2">
-        <v>1.0999999999999999E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>0.60199999999999998</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="C13" s="2">
-        <v>8.0000000000000002E-3</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.60099999999999998</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="C14" s="2">
-        <v>8.9999999999999993E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
-    <sortCondition descending="1" ref="B1:B14"/>
+    <sortCondition ref="A1:A14"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2373,213 +2604,212 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="5"/>
+    <col min="1" max="1" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4" s="4" customFormat="1" ht="19" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1.4E-2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="C4" s="2">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="5">
-        <v>0.63400000000000001</v>
-      </c>
-      <c r="C2" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="5">
-        <v>0.63200000000000001</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="B11" s="2">
+        <v>0.629</v>
+      </c>
+      <c r="C11" s="2">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="5">
+      <c r="D11" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2">
         <v>0.63</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C12" s="2">
         <v>1E-3</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="5">
-        <v>0.629</v>
-      </c>
-      <c r="C5" s="5">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="5">
-        <v>0.60799999999999998</v>
-      </c>
-      <c r="C6" s="5">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="D12" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.193</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5">
-        <v>0.60699999999999998</v>
-      </c>
-      <c r="C7" s="5">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="5">
-        <v>0.58199999999999996</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="5">
-        <v>0.58099999999999996</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1.4E-2</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="5">
+      <c r="B14" s="2">
         <v>0.56200000000000006</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C14" s="2">
         <v>0.19</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="5">
-        <v>0.54400000000000004</v>
-      </c>
-      <c r="C12" s="5">
-        <v>0.193</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="5">
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="5">
-        <v>0.35199999999999998</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0.14899999999999999</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>105</v>
+      <c r="D14" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
-    <sortCondition descending="1" ref="B1:B14"/>
+    <sortCondition ref="A1:A14"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2588,6 +2818,220 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="4" customFormat="1" ht="19" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="C2" s="2">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1.4E-2</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.56299999999999994</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3.1E-2</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
+    <sortCondition ref="A1:A14"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -2596,7 +3040,7 @@
     <col min="5" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2610,406 +3054,198 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="5">
-        <v>0.61599999999999999</v>
-      </c>
-      <c r="C2" s="5">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2">
-        <v>0.60599999999999998</v>
+        <v>0.64</v>
       </c>
       <c r="C3" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.159</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="5">
-        <v>0.60399999999999998</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1.4E-2</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0.59699999999999998</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.58799999999999997</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B10" s="2">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.156</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2">
-        <v>0.57099999999999995</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="B11" s="2">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2.4E-2</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="C13" s="2">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1.2E-2</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0.56899999999999995</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.56299999999999994</v>
-      </c>
-      <c r="C10" s="2">
-        <v>3.1E-2</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.55100000000000005</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="B14" s="2">
+        <v>0.627</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.54</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0.54</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0.53900000000000003</v>
-      </c>
-      <c r="C14" s="2">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
-    <sortCondition descending="1" ref="B1:B14"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="42.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="5">
-        <v>0.71899999999999997</v>
-      </c>
-      <c r="C2" s="5">
-        <v>2.4E-2</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.70899999999999996</v>
-      </c>
-      <c r="C3" s="2">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.69699999999999995</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0.69199999999999995</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.66800000000000004</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0.627</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0.60899999999999999</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.156</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0.57199999999999995</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.57099999999999995</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.159</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.56499999999999995</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.16900000000000001</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.54200000000000004</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.23400000000000001</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0.51300000000000001</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.224</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0.39600000000000002</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0.23400000000000001</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D15">
-    <sortCondition descending="1" ref="B1:B15"/>
+    <sortCondition ref="A1:A14"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
